--- a/data/trans_orig/IP29_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP29_R-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28329</t>
+          <t>27601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45166</t>
+          <t>44044</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29114</t>
+          <t>28972</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46039</t>
+          <t>45743</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60592</t>
+          <t>61345</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84384</t>
+          <t>86324</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87437</t>
+          <t>88559</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104274</t>
+          <t>105002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>99656</t>
+          <t>99952</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>116581</t>
+          <t>116723</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>193914</t>
+          <t>191974</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>217706</t>
+          <t>216953</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>77,96%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55341</t>
+          <t>55097</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75001</t>
+          <t>75371</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49085</t>
+          <t>49652</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69737</t>
+          <t>70209</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110804</t>
+          <t>110659</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137736</t>
+          <t>139102</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,99%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>113779</t>
+          <t>113409</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>133439</t>
+          <t>133683</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>138976</t>
+          <t>138504</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>159628</t>
+          <t>159061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>259757</t>
+          <t>258391</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>286689</t>
+          <t>286834</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,16%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33006</t>
+          <t>32846</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49854</t>
+          <t>49057</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29111</t>
+          <t>29432</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46073</t>
+          <t>46902</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66903</t>
+          <t>67084</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90989</t>
+          <t>89829</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85429</t>
+          <t>86226</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102277</t>
+          <t>102437</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>97781</t>
+          <t>96952</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114743</t>
+          <t>114422</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>188148</t>
+          <t>189308</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>212234</t>
+          <t>212053</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,97%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52423</t>
+          <t>52936</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74992</t>
+          <t>75987</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55169</t>
+          <t>53744</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75266</t>
+          <t>76078</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113859</t>
+          <t>113867</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>144744</t>
+          <t>144837</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,83%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121106</t>
+          <t>120111</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143675</t>
+          <t>143162</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121909</t>
+          <t>121097</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>142006</t>
+          <t>143431</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>248530</t>
+          <t>248437</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>279415</t>
+          <t>279407</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>187669</t>
+          <t>186301</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>226564</t>
+          <t>225741</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>180081</t>
+          <t>180744</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>218392</t>
+          <t>218650</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>379329</t>
+          <t>379490</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>433388</t>
+          <t>432192</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,06%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>426201</t>
+          <t>427024</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>465096</t>
+          <t>466464</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>477045</t>
+          <t>476787</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>515356</t>
+          <t>514693</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>914814</t>
+          <t>916010</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>968873</t>
+          <t>968712</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,85%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35186</t>
+          <t>35227</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53638</t>
+          <t>53478</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34396</t>
+          <t>33007</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54304</t>
+          <t>53277</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73252</t>
+          <t>73657</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>99132</t>
+          <t>99983</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82089</t>
+          <t>82249</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100541</t>
+          <t>100500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94015</t>
+          <t>95042</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113923</t>
+          <t>115312</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>184914</t>
+          <t>184063</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>210794</t>
+          <t>210389</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,07%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44048</t>
+          <t>43448</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62575</t>
+          <t>62662</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39336</t>
+          <t>39664</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58902</t>
+          <t>59251</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88733</t>
+          <t>87756</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117501</t>
+          <t>117543</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>137378</t>
+          <t>137291</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155905</t>
+          <t>156505</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>159232</t>
+          <t>158883</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>178798</t>
+          <t>178470</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>300586</t>
+          <t>300544</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>329354</t>
+          <t>330331</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>79,01%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31313</t>
+          <t>31359</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48674</t>
+          <t>48513</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29491</t>
+          <t>28960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47223</t>
+          <t>46184</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65487</t>
+          <t>64251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89733</t>
+          <t>89814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102029</t>
+          <t>102190</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>119390</t>
+          <t>119344</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>114706</t>
+          <t>115745</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132438</t>
+          <t>132969</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>222898</t>
+          <t>222817</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>247144</t>
+          <t>248380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,45%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41261</t>
+          <t>41928</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63341</t>
+          <t>63534</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36054</t>
+          <t>35962</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57356</t>
+          <t>55957</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83226</t>
+          <t>83398</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111619</t>
+          <t>113952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>145477</t>
+          <t>145284</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>167557</t>
+          <t>166890</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>147651</t>
+          <t>149050</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>168953</t>
+          <t>169045</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>302207</t>
+          <t>299874</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>330600</t>
+          <t>330428</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,85%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>170146</t>
+          <t>167710</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>207315</t>
+          <t>207091</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>155737</t>
+          <t>155443</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>194490</t>
+          <t>193585</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>334877</t>
+          <t>337279</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>392290</t>
+          <t>388911</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>487886</t>
+          <t>488110</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>525055</t>
+          <t>527491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>538899</t>
+          <t>539804</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>577652</t>
+          <t>577946</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1036301</t>
+          <t>1039680</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1093714</t>
+          <t>1091312</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,39%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40233</t>
+          <t>39527</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58532</t>
+          <t>58589</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44599</t>
+          <t>43569</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63755</t>
+          <t>62739</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88953</t>
+          <t>88463</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115989</t>
+          <t>116786</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,37%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72135</t>
+          <t>72078</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90434</t>
+          <t>91140</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81204</t>
+          <t>82220</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100360</t>
+          <t>101390</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>159637</t>
+          <t>158840</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>186673</t>
+          <t>187163</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,9%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51402</t>
+          <t>52714</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72123</t>
+          <t>71929</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59469</t>
+          <t>58659</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82118</t>
+          <t>81411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115882</t>
+          <t>117999</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146586</t>
+          <t>148645</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>130370</t>
+          <t>130564</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>151091</t>
+          <t>149779</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>137627</t>
+          <t>138334</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>160276</t>
+          <t>161086</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>275652</t>
+          <t>273593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>306356</t>
+          <t>304239</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,05%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34919</t>
+          <t>34904</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52449</t>
+          <t>52255</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36870</t>
+          <t>36462</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55252</t>
+          <t>55290</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76140</t>
+          <t>77180</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100967</t>
+          <t>103207</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>100006</t>
+          <t>100200</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117536</t>
+          <t>117551</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>107546</t>
+          <t>107508</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125928</t>
+          <t>126336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>214285</t>
+          <t>212045</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>239112</t>
+          <t>238072</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,52%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36241</t>
+          <t>36597</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57178</t>
+          <t>57106</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42066</t>
+          <t>41024</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62321</t>
+          <t>62081</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82828</t>
+          <t>84478</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112682</t>
+          <t>113954</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,46%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143546</t>
+          <t>143618</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>164483</t>
+          <t>164127</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137322</t>
+          <t>137562</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157577</t>
+          <t>158619</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>287685</t>
+          <t>286413</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>317539</t>
+          <t>315889</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,9%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>181116</t>
+          <t>181939</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>217984</t>
+          <t>218783</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>201162</t>
+          <t>198247</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>240839</t>
+          <t>240145</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,47 +6048,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>27,26%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>33,03%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>420535</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>390945</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>448340</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>29,75%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>27,66%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>33,12%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>420535</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>391273</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>448977</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>29,75%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>27,68%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>468355</t>
+          <t>467556</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>505223</t>
+          <t>504400</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>486306</t>
+          <t>487000</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>525983</t>
+          <t>528898</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,47 +6161,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>72,74%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>992949</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>965144</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1022539</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>70,25%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>68,28%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>72,34%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1464</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>992949</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>964507</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1022211</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>70,25%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>68,24%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>72,32%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP29_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP29_R-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37365</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29658</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>47647</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>25,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20,36%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>32,7%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>35963</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>27601</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>44044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>28043</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>44481</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>27,12%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>33,21%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>37365</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>28972</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>45743</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>25,65%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61345</t>
+          <t>60920</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86324</t>
+          <t>85187</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>108330</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>98048</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>116037</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>74,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>67,3%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>79,64%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>96640</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>88559</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>105002</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>88122</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>104560</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>72,88%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>66,79%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>79,19%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>108330</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>99952</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>116723</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>74,35%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>191974</t>
+          <t>193111</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>216953</t>
+          <t>217378</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,11%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>145695</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>145695</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>145695</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>132603</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>132603</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>132603</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>145695</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>145695</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>145695</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>59672</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>48298</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>68951</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>28,59%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>23,14%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>33,04%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>64911</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>55097</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>75371</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>54570</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>76185</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>34,38%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>29,19%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>39,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>59672</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>49652</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>70209</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>28,59%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110659</t>
+          <t>110213</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>139102</t>
+          <t>139667</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>149041</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>139762</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>160415</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>71,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>66,96%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>76,86%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>123869</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>113409</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>133683</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>112595</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>134210</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>65,62%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>60,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>70,81%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>149041</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>138504</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>159061</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>71,41%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>258391</t>
+          <t>257826</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>286834</t>
+          <t>287280</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,27%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>208713</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>208713</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>208713</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>302</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>188780</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>188780</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>188780</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>208713</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>208713</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>208713</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37532</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>29778</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>46458</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>26,09%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>20,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>32,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>40681</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>32846</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>49057</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>33505</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>49564</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>30,07%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>24,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>37532</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>29432</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>46902</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>26,09%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67084</t>
+          <t>66710</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89829</t>
+          <t>89913</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>106322</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>97396</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>114076</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>73,91%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>67,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>79,3%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>94602</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>86226</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>102437</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>85719</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>101778</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>69,93%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>63,74%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>75,72%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>106322</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>96952</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>114422</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>73,91%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>189308</t>
+          <t>189224</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>212053</t>
+          <t>212427</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,1%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>143854</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>143854</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>143854</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>135283</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>135283</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>135283</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>143854</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>143854</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>143854</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>64265</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>54220</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>75985</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>32,59%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>27,5%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>38,54%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>63545</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>52936</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>75987</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>53348</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>75539</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>32,4%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>26,99%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>38,75%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>64265</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>53744</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>76078</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>32,59%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113867</t>
+          <t>112751</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>144837</t>
+          <t>143471</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,48%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>132910</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>121190</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>142955</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>67,41%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>61,46%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>72,5%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>132553</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>120111</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>143162</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>120559</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>142750</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>67,6%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>61,25%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>73,01%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>132910</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>121097</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>143431</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>67,41%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>248437</t>
+          <t>249803</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>279407</t>
+          <t>280523</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,33%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197175</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197175</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197175</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>196098</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>196098</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>196098</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>197175</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>197175</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>197175</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>198834</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>179601</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>218963</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>28,59%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>25,83%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>31,49%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>205100</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>186301</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>225741</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>186056</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>223047</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>31,42%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28,54%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>34,58%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>198834</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>180744</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>218650</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>28,59%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>379490</t>
+          <t>377129</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>432192</t>
+          <t>432518</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>496603</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>476474</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>515836</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>71,41%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>68,51%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>74,17%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>671</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>447665</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>427024</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>466464</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>429718</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>466709</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>68,58%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>65,42%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>71,46%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>746</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>496603</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>476787</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>514693</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>71,41%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>916010</t>
+          <t>915684</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>968712</t>
+          <t>971073</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>72,03%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>695437</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>695437</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>695437</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>977</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>652765</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>652765</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>652765</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1046</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>695437</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>695437</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>695437</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>42754</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>33304</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>52471</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>28,83%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>22,45%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>35,38%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>43259</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>35227</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>53478</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>34151</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>52881</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>31,87%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25,95%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,4%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>42754</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>33007</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>53277</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>28,83%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73657</t>
+          <t>73359</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>99983</t>
+          <t>98900</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>34,82%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>105565</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>95848</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>115015</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>71,17%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>64,62%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>77,55%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>92468</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>82249</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>100500</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>82846</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>101576</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>68,13%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>60,6%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>74,05%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>105565</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>95042</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>115312</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>71,17%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>184063</t>
+          <t>185146</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>210389</t>
+          <t>210687</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,17%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148319</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148319</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148319</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>135727</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>135727</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>135727</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148319</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148319</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148319</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>49103</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>38774</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>60229</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>22,51%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17,78%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>27,61%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>53043</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>43448</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>62662</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>44202</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>62771</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>26,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>21,73%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>31,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>49103</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>39664</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>59251</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>22,51%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87756</t>
+          <t>89166</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117543</t>
+          <t>118235</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>169031</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>157905</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>179360</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>77,49%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>72,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>82,22%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>146910</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>137291</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>156505</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>137182</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>155751</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>73,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>68,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>78,27%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>169031</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>158883</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>178470</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>77,49%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>300544</t>
+          <t>299852</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>330331</t>
+          <t>328921</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>78,67%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>218134</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>218134</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>218134</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>309</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>199953</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>199953</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>199953</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>218134</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>218134</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>218134</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37281</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>28415</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>46632</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23,02%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>17,55%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>28,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>39674</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>31359</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>48513</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>30402</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>48073</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>26,33%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,81%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>32,19%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>37281</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>28960</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>46184</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>23,02%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64251</t>
+          <t>65369</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89814</t>
+          <t>89706</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>124648</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>115297</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>133514</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>76,98%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>71,2%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>82,45%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>111029</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>102190</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>119344</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>102630</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>120301</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>73,67%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>67,81%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>79,19%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>124648</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>115745</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>132969</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>76,98%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>222817</t>
+          <t>222925</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>248380</t>
+          <t>247262</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,09%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>161929</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>161929</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>161929</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>150703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>150703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>150703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>161929</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>161929</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>161929</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>45346</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35230</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>56392</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22,12%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17,18%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>27,51%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>51934</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>41928</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>63534</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>41561</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>62416</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>24,87%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20,08%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>30,43%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>45346</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>35962</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>55957</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>22,12%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83398</t>
+          <t>83189</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113952</t>
+          <t>113627</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,46%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>159661</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>148615</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>169777</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>77,88%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>72,49%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>82,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>156884</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>145284</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>166890</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>146402</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>167257</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>75,13%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>69,57%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>79,92%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>159661</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>149050</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>169045</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>77,88%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>299874</t>
+          <t>300199</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>330428</t>
+          <t>330637</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,9%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205007</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205007</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205007</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>273</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>208818</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>208818</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>208818</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205007</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205007</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205007</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>174484</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>156425</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>193734</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>23,79%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>21,33%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>26,42%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>187911</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>167710</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>207091</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>167451</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>205543</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>27,03%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>24,12%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>29,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>174484</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>155443</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>193585</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>23,79%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>337279</t>
+          <t>333567</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>388911</t>
+          <t>390742</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>558905</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>539655</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>576964</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>76,21%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>73,58%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>78,67%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>732</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>507290</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>488110</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>527491</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>489658</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>527750</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>72,97%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>70,21%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>75,88%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>807</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>558905</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>539804</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>577946</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>76,21%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1039680</t>
+          <t>1037849</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1091312</t>
+          <t>1095024</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,65%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>733389</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>733389</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>733389</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1001</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>695201</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>695201</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>695201</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1047</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>733389</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>733389</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>733389</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>53628</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>44567</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>65126</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30,74%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>44,93%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>48988</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>39527</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>58589</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>39602</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>58547</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>37,49%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>30,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>44,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>53628</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>43569</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>62739</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>37,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88463</t>
+          <t>88034</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116786</t>
+          <t>115882</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,04%</t>
         </is>
       </c>
     </row>
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>91331</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>79833</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>100392</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>63,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>55,07%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>69,26%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>81679</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>72078</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>91140</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>72120</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>91065</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>62,51%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>55,16%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>69,75%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>91331</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>82220</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>101390</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>63,0%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158840</t>
+          <t>159744</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>187163</t>
+          <t>187592</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>68,06%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>144959</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>144959</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>144959</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>130667</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>130667</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>130667</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>144959</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>144959</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>144959</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>69846</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>59060</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>81098</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>31,79%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>26,88%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>36,91%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>61752</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>52714</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>71929</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>52308</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>72264</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>30,5%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>26,03%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>35,52%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>69846</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>58659</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>81411</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>31,79%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117999</t>
+          <t>117348</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>148645</t>
+          <t>147446</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>149899</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>138647</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>160685</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>68,21%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>63,09%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>73,12%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>140741</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>130564</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>149779</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>130229</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>150185</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>69,5%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>64,48%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>73,97%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>149899</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>138334</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>161086</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>68,21%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>273593</t>
+          <t>274792</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>304239</t>
+          <t>304890</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,21%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>219745</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>219745</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>219745</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>326</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>202493</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>202493</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>202493</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>219745</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>219745</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>219745</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>45927</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>36793</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>54616</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>28,21%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>22,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>33,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>42929</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>34904</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>52255</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>34824</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>51969</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>28,16%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,28%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>45927</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>36462</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>55290</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>28,21%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77180</t>
+          <t>74882</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103207</t>
+          <t>101502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>116871</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>108182</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>126005</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>71,79%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>66,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>77,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>109526</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>100200</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>117551</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>100486</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>117631</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>71,84%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>65,72%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>77,11%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>116871</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>107508</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>126336</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>71,79%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>212045</t>
+          <t>213750</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>238072</t>
+          <t>240370</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>76,25%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>162798</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>162798</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>162798</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>152455</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>152455</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>152455</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>162798</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>162798</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>162798</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>51353</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>41587</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>61735</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>25,72%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20,83%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>30,92%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>46112</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>36597</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>57106</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>57022</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>22,97%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,23%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>28,45%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>51353</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>41024</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>62081</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>25,72%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84478</t>
+          <t>82431</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113954</t>
+          <t>112220</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>148290</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>137908</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>158056</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>74,28%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>69,08%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>79,17%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>154612</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>143618</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>164127</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>143702</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>164560</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>77,03%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>71,55%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>81,77%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>148290</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>137562</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>158619</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>74,28%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>286413</t>
+          <t>288147</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>315889</t>
+          <t>317936</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,41%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>199643</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>199643</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>199643</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>200724</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>200724</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>200724</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>199643</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>199643</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>199643</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>220754</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>200495</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>243531</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>30,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>27,57%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>33,49%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>301</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>199781</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>181939</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>218783</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>181532</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>220370</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>29,11%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>26,51%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>31,88%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>220754</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>198247</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>240145</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>30,36%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>390945</t>
+          <t>393370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>448340</t>
+          <t>449071</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,77%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>506391</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>483614</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>526650</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>69,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>66,51%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>72,43%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>733</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>486558</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>467556</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>504400</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>465969</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>504807</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>70,89%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>68,12%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>73,49%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>731</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>506391</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>487000</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>528898</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>69,64%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>965144</t>
+          <t>964413</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1022539</t>
+          <t>1020114</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,17%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>727145</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>727145</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>727145</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1034</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>686339</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>686339</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>686339</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>727145</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>727145</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>727145</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
